--- a/etf_holdings/2026-09-14_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-14_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1116,106 +1116,394 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2603</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>長榮</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.99%</t>
-        </is>
-      </c>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.94%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
-        <v>1169000</v>
-      </c>
+      <c r="J12" t="n">
+        <v>172000</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-13_00400A_full_holdings.xlsx</t>
+          <t>2026-09-13_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.91%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>236000</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-09-13_00990A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-09-13_00405A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>弘塑</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.26%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>30000</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-09-13_00405A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>5.92%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>4.71%</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-1.21%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>468000</v>
+      </c>
+      <c r="K16" t="n">
+        <v>378000</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-90,000</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-09-13_00405A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>10TX台指期貨</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1.71%</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>19</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-09-13_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>00400A</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2603</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>長榮</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.99%</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>1169000</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-09-13_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>3008</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>大立光</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>大立光</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>0.95%</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>0.84%</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>-0.11%</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J19" t="n">
         <v>40000</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K19" t="n">
         <v>39000</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>-1,000</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>2026-09-13_00400A_full_holdings.xlsx</t>
         </is>
